--- a/Assets/test260903/chapter0101.xlsx
+++ b/Assets/test260903/chapter0101.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_78D6C523542A8DBFC7C17204B70FFA00F94AF2BB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6D60EC0-C902-477F-A047-498280243F73}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="chapter0101" sheetId="1" r:id="rId4"/>
+    <sheet name="chapter0101" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="L8TtcbOrmm8sH2DBXQgaWUa2YyVEYkQrP3FpebYLDkY="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="163">
   <si>
     <t>Command</t>
   </si>
@@ -230,13 +239,7 @@
     <t>けれど……</t>
   </si>
   <si>
-    <t>*選択肢0101-2-a</t>
-  </si>
-  <si>
     <t>ごめん……まだ書き上がってない</t>
-  </si>
-  <si>
-    <t>*選択肢0101-2-b</t>
   </si>
   <si>
     <t>傑作を作るには、時間がかかる</t>
@@ -551,31 +554,94 @@
   </si>
   <si>
     <t>*chapter0102_Start</t>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0101-2-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0101-2-b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>浪川有希</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>通常</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Jump</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0101-2合流</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0101-8-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0101-1合流</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0101-1-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0101-1-b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0101-8合流</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -584,43 +650,49 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -810,28 +882,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1061"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.5"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="7" width="5.13"/>
-    <col customWidth="1" min="8" max="8" width="8.63"/>
-    <col customWidth="1" min="9" max="9" width="37.75"/>
-    <col customWidth="1" min="10" max="10" width="8.25"/>
-    <col customWidth="1" min="11" max="11" width="6.0"/>
-    <col customWidth="1" min="12" max="12" width="11.38"/>
-    <col customWidth="1" min="13" max="26" width="8.0"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="7" width="5.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:12" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -869,8 +941,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1"/>
@@ -878,29 +950,29 @@
       <c r="I2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
+    <row r="3" spans="1:12" ht="13.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="1"/>
-      <c r="H4" s="3">
-        <v>3.0</v>
+      <c r="H4" s="1">
+        <v>3</v>
       </c>
       <c r="I4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
+    <row r="5" spans="1:12" ht="13.5" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -909,7 +981,7 @@
       <c r="I5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
+    <row r="6" spans="1:12" ht="13.5" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -920,7 +992,7 @@
       <c r="I6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" ht="13.5" customHeight="1">
+    <row r="7" spans="1:12" ht="13.5" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -930,61 +1002,61 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" ht="13.5" customHeight="1">
+    <row r="8" spans="1:12" ht="13.5" customHeight="1">
       <c r="I8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1">
+    <row r="9" spans="1:12" ht="13.5" customHeight="1">
       <c r="I9" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1">
+    <row r="10" spans="1:12" ht="13.5" customHeight="1">
       <c r="I10" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1">
+    <row r="11" spans="1:12" ht="13.5" customHeight="1">
       <c r="I11" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1">
+    <row r="12" spans="1:12" ht="13.5" customHeight="1">
       <c r="I12" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="13.5" customHeight="1">
+    <row r="13" spans="1:12" ht="13.5" customHeight="1">
       <c r="I13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1">
+    <row r="14" spans="1:12" ht="13.5" customHeight="1">
       <c r="I14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" ht="13.5" customHeight="1">
+    <row r="15" spans="1:12" ht="13.5" customHeight="1">
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" ht="13.5" customHeight="1">
+    <row r="16" spans="1:12" ht="13.5" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="G16" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
+    <row r="17" spans="1:10" ht="13.5" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -995,7 +1067,7 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" ht="13.5" customHeight="1">
+    <row r="18" spans="1:10" ht="13.5" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
@@ -1006,7 +1078,7 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" ht="13.5" customHeight="1">
+    <row r="19" spans="1:10" ht="13.5" customHeight="1">
       <c r="B19" s="1" t="s">
         <v>32</v>
       </c>
@@ -1018,43 +1090,43 @@
       </c>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" ht="13.5" customHeight="1">
+    <row r="20" spans="1:10" ht="13.5" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" ht="13.5" customHeight="1">
+    <row r="21" spans="1:10" ht="13.5" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="1" t="s">
         <v>37</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1">
+    <row r="22" spans="1:10" ht="13.5" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>37</v>
+    <row r="23" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" ht="13.5" customHeight="1">
+    <row r="24" spans="1:10" ht="13.5" customHeight="1">
       <c r="B24" s="1" t="s">
         <v>32</v>
       </c>
@@ -1065,7 +1137,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" ht="13.5" customHeight="1">
+    <row r="25" spans="1:10" ht="13.5" customHeight="1">
       <c r="B25" s="1" t="s">
         <v>32</v>
       </c>
@@ -1076,26 +1148,26 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" ht="13.5" customHeight="1">
+    <row r="26" spans="1:10" ht="13.5" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>45</v>
+        <v>156</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A27" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
-    <row r="28" ht="13.5" customHeight="1">
+    <row r="28" spans="1:10" ht="13.5" customHeight="1">
       <c r="B28" s="1" t="s">
-        <v>32</v>
+        <v>154</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>33</v>
@@ -1104,75 +1176,75 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1">
+    <row r="29" spans="1:10" ht="13.5" customHeight="1">
       <c r="B29" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>33</v>
+        <v>155</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" ht="13.5" customHeight="1">
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="1" t="s">
         <v>45</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
-    <row r="31" ht="13.5" customHeight="1">
-      <c r="A31" s="3" t="s">
-        <v>45</v>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A31" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
-    <row r="32" ht="13.5" customHeight="1">
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
       <c r="I32" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" ht="13.5" customHeight="1">
+    <row r="33" spans="1:9" ht="13.5" customHeight="1">
       <c r="I33" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="34" ht="13.5" customHeight="1">
+    <row r="34" spans="1:9" ht="13.5" customHeight="1">
       <c r="I34" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" ht="13.5" customHeight="1">
+    <row r="35" spans="1:9" ht="13.5" customHeight="1">
       <c r="I35" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="36" ht="13.5" customHeight="1">
+    <row r="36" spans="1:9" ht="13.5" customHeight="1">
       <c r="I36" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" ht="13.5" customHeight="1">
+    <row r="37" spans="1:9" ht="13.5" customHeight="1">
       <c r="I37" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" ht="13.5" customHeight="1">
+    <row r="38" spans="1:9" ht="13.5" customHeight="1">
       <c r="I38" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="39" ht="13.5" customHeight="1">
+    <row r="39" spans="1:9" ht="13.5" customHeight="1">
       <c r="I39" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="40" ht="13.5" customHeight="1">
+    <row r="40" spans="1:9" ht="13.5" customHeight="1">
       <c r="B40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1183,7 +1255,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="41" ht="13.5" customHeight="1">
+    <row r="41" spans="1:9" ht="13.5" customHeight="1">
       <c r="B41" s="1" t="s">
         <v>32</v>
       </c>
@@ -1194,61 +1266,61 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" ht="13.5" customHeight="1">
+    <row r="42" spans="1:9" ht="13.5" customHeight="1">
       <c r="I42" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="43" ht="13.5" customHeight="1">
+    <row r="43" spans="1:9" ht="13.5" customHeight="1">
       <c r="I43" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="44" ht="13.5" customHeight="1">
+    <row r="44" spans="1:9" ht="13.5" customHeight="1">
       <c r="I44" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="45" ht="13.5" customHeight="1">
+    <row r="45" spans="1:9" ht="13.5" customHeight="1">
       <c r="I45" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="46" ht="13.5" customHeight="1">
+    <row r="46" spans="1:9" ht="13.5" customHeight="1">
       <c r="I46" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="47" ht="13.5" customHeight="1">
+    <row r="47" spans="1:9" ht="13.5" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B47" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" ht="13.5" customHeight="1">
+    </row>
+    <row r="48" spans="1:9" ht="13.5" customHeight="1">
       <c r="A48" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>65</v>
+      <c r="B48" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" ht="13.5" customHeight="1">
-      <c r="A49" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A49" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" ht="13.5" customHeight="1">
+    <row r="50" spans="1:10" ht="13.5" customHeight="1">
       <c r="B50" s="1" t="s">
         <v>32</v>
       </c>
@@ -1256,10 +1328,10 @@
         <v>33</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="51" ht="13.5" customHeight="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="13.5" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>32</v>
       </c>
@@ -1267,11 +1339,11 @@
         <v>33</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" ht="13.5" customHeight="1">
+    <row r="52" spans="1:10" ht="13.5" customHeight="1">
       <c r="B52" s="1" t="s">
         <v>32</v>
       </c>
@@ -1279,115 +1351,115 @@
         <v>33</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" ht="13.5" customHeight="1">
+    <row r="53" spans="1:10" ht="13.5" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>70</v>
+        <v>156</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="3" t="s">
-        <v>65</v>
+    <row r="54" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A54" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" ht="13.5" customHeight="1">
+    <row r="55" spans="1:10" ht="13.5" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>32</v>
+        <v>154</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B56" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="56" ht="13.5" customHeight="1">
-      <c r="B56" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="57" ht="13.5" customHeight="1">
+    </row>
+    <row r="57" spans="1:10" ht="13.5" customHeight="1">
       <c r="A57" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>70</v>
+      <c r="B57" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="I57" s="1"/>
     </row>
-    <row r="58" ht="13.5" customHeight="1">
-      <c r="A58" s="3" t="s">
-        <v>70</v>
+    <row r="58" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A58" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="I58" s="1"/>
     </row>
-    <row r="59" ht="13.5" customHeight="1">
+    <row r="59" spans="1:10" ht="13.5" customHeight="1">
       <c r="I59" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" ht="13.5" customHeight="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="13.5" customHeight="1">
       <c r="I60" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="61" ht="13.5" customHeight="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="13.5" customHeight="1">
       <c r="A61" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>76</v>
+      <c r="B61" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="62" ht="13.5" customHeight="1">
-      <c r="A62" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A62" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="B62" s="1"/>
       <c r="I62" s="1"/>
     </row>
-    <row r="63" ht="13.5" customHeight="1">
+    <row r="63" spans="1:10" ht="13.5" customHeight="1">
       <c r="B63" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="64" ht="13.5" customHeight="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="13.5" customHeight="1">
       <c r="B64" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65" ht="13.5" customHeight="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="13.5" customHeight="1">
       <c r="B65" s="1" t="s">
         <v>32</v>
       </c>
@@ -1395,10 +1467,10 @@
         <v>41</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="66" ht="13.5" customHeight="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="13.5" customHeight="1">
       <c r="B66" s="1" t="s">
         <v>32</v>
       </c>
@@ -1406,29 +1478,29 @@
         <v>41</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="67" ht="13.5" customHeight="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="13.5" customHeight="1">
       <c r="A67" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>82</v>
+      <c r="B67" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="68" ht="13.5" customHeight="1">
-      <c r="A68" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A68" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="B68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" ht="13.5" customHeight="1">
+    <row r="69" spans="1:9" ht="13.5" customHeight="1">
       <c r="B69" s="1" t="s">
         <v>32</v>
       </c>
@@ -1436,10 +1508,10 @@
         <v>33</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="70" ht="13.5" customHeight="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="13.5" customHeight="1">
       <c r="B70" s="1" t="s">
         <v>32</v>
       </c>
@@ -1447,29 +1519,29 @@
         <v>33</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="71" ht="13.5" customHeight="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="13.5" customHeight="1">
       <c r="A71" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>86</v>
+      <c r="B71" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="72" ht="13.5" customHeight="1">
-      <c r="A72" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A72" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="B72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
     </row>
-    <row r="73" ht="13.5" customHeight="1">
+    <row r="73" spans="1:9" ht="13.5" customHeight="1">
       <c r="B73" s="1" t="s">
         <v>32</v>
       </c>
@@ -1477,10 +1549,10 @@
         <v>33</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="74" ht="13.5" customHeight="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="13.5" customHeight="1">
       <c r="B74" s="1" t="s">
         <v>32</v>
       </c>
@@ -1488,10 +1560,10 @@
         <v>33</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="75" ht="13.5" customHeight="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="13.5" customHeight="1">
       <c r="B75" s="1" t="s">
         <v>32</v>
       </c>
@@ -1499,10 +1571,10 @@
         <v>41</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="76" ht="13.5" customHeight="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="13.5" customHeight="1">
       <c r="B76" s="1" t="s">
         <v>32</v>
       </c>
@@ -1510,10 +1582,10 @@
         <v>41</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="77" ht="13.5" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="13.5" customHeight="1">
       <c r="B77" s="1" t="s">
         <v>32</v>
       </c>
@@ -1521,10 +1593,10 @@
         <v>41</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="78" ht="13.5" customHeight="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="13.5" customHeight="1">
       <c r="B78" s="1" t="s">
         <v>32</v>
       </c>
@@ -1532,10 +1604,10 @@
         <v>41</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="79" ht="13.5" customHeight="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="13.5" customHeight="1">
       <c r="B79" s="1" t="s">
         <v>32</v>
       </c>
@@ -1543,10 +1615,10 @@
         <v>41</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="80" ht="13.5" customHeight="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="13.5" customHeight="1">
       <c r="B80" s="1" t="s">
         <v>32</v>
       </c>
@@ -1554,10 +1626,10 @@
         <v>33</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="81" ht="13.5" customHeight="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
       <c r="B81" s="1" t="s">
         <v>32</v>
       </c>
@@ -1565,55 +1637,55 @@
         <v>33</v>
       </c>
       <c r="I81" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J81" s="1"/>
+    </row>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I82" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I83" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J81" s="1"/>
-    </row>
-    <row r="82" ht="13.5" customHeight="1">
-      <c r="I82" s="1" t="s">
+    </row>
+    <row r="84" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I84" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="83" ht="13.5" customHeight="1">
-      <c r="I83" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="84" ht="13.5" customHeight="1">
-      <c r="I84" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="85" ht="13.5" customHeight="1">
+    <row r="85" spans="1:10" ht="13.5" customHeight="1">
       <c r="A85" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>100</v>
+      <c r="B85" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J85" s="1"/>
     </row>
-    <row r="86" ht="13.5" customHeight="1">
+    <row r="86" spans="1:10" ht="13.5" customHeight="1">
       <c r="A86" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>102</v>
+      <c r="B86" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J86" s="1"/>
     </row>
-    <row r="87" ht="13.5" customHeight="1">
-      <c r="A87" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="88" ht="13.5" customHeight="1">
+    <row r="87" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A87" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="13.5" customHeight="1">
       <c r="B88" s="1" t="s">
         <v>32</v>
       </c>
@@ -1621,10 +1693,10 @@
         <v>41</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="89" ht="13.5" customHeight="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="13.5" customHeight="1">
       <c r="B89" s="1" t="s">
         <v>32</v>
       </c>
@@ -1632,10 +1704,10 @@
         <v>41</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="90" ht="13.5" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="13.5" customHeight="1">
       <c r="B90" s="1" t="s">
         <v>32</v>
       </c>
@@ -1643,10 +1715,10 @@
         <v>41</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="91" ht="13.5" customHeight="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="13.5" customHeight="1">
       <c r="B91" s="1" t="s">
         <v>32</v>
       </c>
@@ -1654,23 +1726,23 @@
         <v>33</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="92" ht="13.5" customHeight="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="13.5" customHeight="1">
       <c r="A92" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="93" ht="13.5" customHeight="1">
-      <c r="A93" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="94" ht="13.5" customHeight="1">
+      <c r="B92" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A93" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
       <c r="B94" s="1" t="s">
         <v>32</v>
       </c>
@@ -1678,10 +1750,10 @@
         <v>33</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="95" ht="13.5" customHeight="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
       <c r="B95" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,10 +1761,10 @@
         <v>33</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="96" ht="13.5" customHeight="1">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
       <c r="B96" s="1" t="s">
         <v>32</v>
       </c>
@@ -1700,10 +1772,10 @@
         <v>33</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="97" ht="13.5" customHeight="1">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="13.5" customHeight="1">
       <c r="B97" s="1" t="s">
         <v>32</v>
       </c>
@@ -1711,62 +1783,62 @@
         <v>33</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="98" ht="13.5" customHeight="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="13.5" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="99" ht="13.5" customHeight="1">
-      <c r="A99" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="100" ht="13.5" customHeight="1">
+      <c r="B98" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A99" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="13.5" customHeight="1">
       <c r="I100" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="101" ht="13.5" customHeight="1">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="13.5" customHeight="1">
       <c r="I101" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="102" ht="13.5" customHeight="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="13.5" customHeight="1">
       <c r="A102" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B102" s="3" t="s">
-        <v>115</v>
+      <c r="B102" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="103" ht="13.5" customHeight="1">
-      <c r="A103" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A103" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
     </row>
-    <row r="104" ht="13.5" customHeight="1">
+    <row r="104" spans="1:9" ht="13.5" customHeight="1">
       <c r="B104" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="105" ht="13.5" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="13.5" customHeight="1">
       <c r="B105" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,41 +1846,41 @@
         <v>33</v>
       </c>
       <c r="I105" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B106" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I107" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="106" ht="13.5" customHeight="1">
-      <c r="B106" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I106" s="1" t="s">
+    <row r="108" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I108" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="107" ht="13.5" customHeight="1">
-      <c r="I107" s="1" t="s">
+    <row r="109" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I109" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="108" ht="13.5" customHeight="1">
-      <c r="I108" s="1" t="s">
+    <row r="110" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I110" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="109" ht="13.5" customHeight="1">
-      <c r="I109" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="110" ht="13.5" customHeight="1">
-      <c r="I110" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="111" ht="13.5" customHeight="1">
+    <row r="111" spans="1:9" ht="13.5" customHeight="1">
       <c r="B111" s="1" t="s">
         <v>32</v>
       </c>
@@ -1816,10 +1888,10 @@
         <v>33</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="112" ht="13.5" customHeight="1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="13.5" customHeight="1">
       <c r="B112" s="1" t="s">
         <v>32</v>
       </c>
@@ -1827,10 +1899,10 @@
         <v>33</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="113" ht="13.5" customHeight="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="13.5" customHeight="1">
       <c r="B113" s="1" t="s">
         <v>32</v>
       </c>
@@ -1838,87 +1910,87 @@
         <v>33</v>
       </c>
       <c r="I113" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B114" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B115" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="114" ht="13.5" customHeight="1">
-      <c r="B114" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I114" s="1" t="s">
+      <c r="I115" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="115" ht="13.5" customHeight="1">
-      <c r="B115" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C115" s="1" t="s">
+    <row r="116" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A116" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J116" s="1"/>
+    </row>
+    <row r="117" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A117" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J117" s="1"/>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A118" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="116" ht="13.5" customHeight="1">
-      <c r="A116" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J116" s="1"/>
-    </row>
-    <row r="117" ht="13.5" customHeight="1">
-      <c r="A117" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J117" s="1"/>
-    </row>
-    <row r="118" ht="13.5" customHeight="1">
-      <c r="A118" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
     </row>
-    <row r="119" ht="13.5" customHeight="1">
+    <row r="119" spans="1:10" ht="13.5" customHeight="1">
       <c r="B119" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="120" ht="13.5" customHeight="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="13.5" customHeight="1">
       <c r="A120" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B120" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="121" ht="13.5" customHeight="1">
-      <c r="A121" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="122" ht="13.5" customHeight="1">
+      <c r="B120" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A121" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="B122" s="1" t="s">
         <v>32</v>
       </c>
@@ -1926,21 +1998,21 @@
         <v>41</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="123" ht="13.5" customHeight="1">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="13.5" customHeight="1">
       <c r="B123" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="124" ht="13.5" customHeight="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="13.5" customHeight="1">
       <c r="B124" s="1" t="s">
         <v>32</v>
       </c>
@@ -1948,26 +2020,26 @@
         <v>41</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="125" ht="13.5" customHeight="1">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="13.5" customHeight="1">
       <c r="A125" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B125" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="126" ht="13.5" customHeight="1">
-      <c r="A126" s="3" t="s">
-        <v>136</v>
+      <c r="B125" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A126" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="B126" s="1"/>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
     </row>
-    <row r="127" ht="13.5" customHeight="1">
+    <row r="127" spans="1:10" ht="13.5" customHeight="1">
       <c r="B127" s="1" t="s">
         <v>32</v>
       </c>
@@ -1975,10 +2047,10 @@
         <v>33</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="128" ht="13.5" customHeight="1">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="13.5" customHeight="1">
       <c r="B128" s="1" t="s">
         <v>32</v>
       </c>
@@ -1986,38 +2058,38 @@
         <v>33</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="129" ht="13.5" customHeight="1">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="13.5" customHeight="1">
       <c r="A129" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A130" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I131" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="130" ht="13.5" customHeight="1">
-      <c r="A130" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="131" ht="13.5" customHeight="1">
-      <c r="I131" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="132" ht="13.5" customHeight="1">
+    <row r="132" spans="1:9" ht="13.5" customHeight="1">
       <c r="A132" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="133" ht="13.5" customHeight="1">
+    <row r="133" spans="1:9" ht="13.5" customHeight="1">
       <c r="A133" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="134" ht="13.5" customHeight="1">
+    <row r="134" spans="1:9" ht="13.5" customHeight="1">
       <c r="A134" s="1" t="s">
         <v>18</v>
       </c>
@@ -2027,57 +2099,57 @@
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
     </row>
-    <row r="135" ht="13.5" customHeight="1">
+    <row r="135" spans="1:9" ht="13.5" customHeight="1">
       <c r="A135" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
     </row>
-    <row r="136" ht="13.5" customHeight="1">
+    <row r="136" spans="1:9" ht="13.5" customHeight="1">
       <c r="I136" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I137" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I138" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="137" ht="13.5" customHeight="1">
-      <c r="I137" s="1" t="s">
+    <row r="139" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I139" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="138" ht="13.5" customHeight="1">
-      <c r="I138" s="1" t="s">
+    <row r="140" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I140" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="139" ht="13.5" customHeight="1">
-      <c r="I139" s="1" t="s">
+    <row r="141" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I141" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="140" ht="13.5" customHeight="1">
-      <c r="I140" s="1" t="s">
+    <row r="142" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I142" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="141" ht="13.5" customHeight="1">
-      <c r="I141" s="1" t="s">
+    <row r="143" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A143" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B143" s="3" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="142" ht="13.5" customHeight="1">
-      <c r="I142" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="143" ht="13.5" customHeight="1">
-      <c r="A143" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="144" ht="13.5" customHeight="1"/>
+    <row r="144" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="145" ht="13.5" customHeight="1"/>
     <row r="146" ht="13.5" customHeight="1"/>
     <row r="147" ht="13.5" customHeight="1"/>
@@ -2996,9 +3068,8 @@
     <row r="1060" ht="13.5" customHeight="1"/>
     <row r="1061" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/test260903/chapter0101.xlsx
+++ b/Assets/test260903/chapter0101.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_78D6C523542A8DBFC7C17204B70FFA00F94AF2BB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6D60EC0-C902-477F-A047-498280243F73}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_78D6C523542A8DBFC7C17204B70FFA00F94AF2BB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB54BD89-8928-4C74-B02F-DD38AC978ABC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,9 +78,6 @@
     <t>BgOff</t>
   </si>
   <si>
-    <t>背景：通学路</t>
-  </si>
-  <si>
     <t>Bgm</t>
   </si>
   <si>
@@ -550,12 +547,6 @@
 SNS内のトレンドにも入っていた</t>
   </si>
   <si>
-    <t>&lt;b&gt;&lt;color=red&gt;それは、崖から落ちる有希の動画だった&lt;/color&gt;&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>*chapter0102_Start</t>
-  </si>
-  <si>
     <t>Selection</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -601,6 +592,18 @@
   </si>
   <si>
     <t>*選択肢0101-8合流</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*chapter0102_Start</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：通学路</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;&lt;color=red&gt;それは、崖から落ちる有希の動画だった&lt;/color&gt;&lt;/b&gt;</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -986,7 +989,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -994,59 +997,59 @@
     </row>
     <row r="7" spans="1:12" ht="13.5" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:12" ht="13.5" customHeight="1">
       <c r="I8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="13.5" customHeight="1">
       <c r="I9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="13.5" customHeight="1">
       <c r="I10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="13.5" customHeight="1">
       <c r="I11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="13.5" customHeight="1">
       <c r="I12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="13.5" customHeight="1">
       <c r="I13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="13.5" customHeight="1">
       <c r="I14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:12" ht="13.5" customHeight="1">
       <c r="I15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:12" ht="13.5" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1058,10 +1061,10 @@
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1"/>
       <c r="I17" s="1"/>
@@ -1069,10 +1072,10 @@
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1">
       <c r="A18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="C18" s="1"/>
       <c r="I18" s="1"/>
@@ -1080,421 +1083,421 @@
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1">
       <c r="B19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="1"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1">
       <c r="A21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1">
       <c r="B24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1">
       <c r="B25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I25" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1">
       <c r="A26" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1">
       <c r="B28" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1">
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1">
       <c r="A30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1">
       <c r="I32" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1">
       <c r="I33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1">
       <c r="I34" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1">
       <c r="I35" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1">
       <c r="I36" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="13.5" customHeight="1">
       <c r="I37" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="13.5" customHeight="1">
       <c r="I38" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="13.5" customHeight="1">
       <c r="I39" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="13.5" customHeight="1">
       <c r="B40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I40" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="13.5" customHeight="1">
       <c r="B41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I41" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="13.5" customHeight="1">
       <c r="I42" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="13.5" customHeight="1">
       <c r="I43" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="13.5" customHeight="1">
       <c r="I44" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="13.5" customHeight="1">
       <c r="I45" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="13.5" customHeight="1">
       <c r="I46" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="13.5" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="13.5" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="13.5" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" customHeight="1">
       <c r="B50" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I50" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="13.5" customHeight="1">
       <c r="B51" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I51" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J51" s="1"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1">
       <c r="B52" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I52" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1">
       <c r="B56" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I57" s="1"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I58" s="1"/>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1">
       <c r="I59" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1">
       <c r="I60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I61" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B62" s="1"/>
       <c r="I62" s="1"/>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1">
       <c r="B63" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1">
       <c r="B64" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="13.5" customHeight="1">
       <c r="B65" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="13.5" customHeight="1">
       <c r="B66" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="13.5" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I67" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="13.5" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B68" s="1"/>
       <c r="H68" s="1"/>
@@ -1502,40 +1505,40 @@
     </row>
     <row r="69" spans="1:9" ht="13.5" customHeight="1">
       <c r="B69" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I69" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="13.5" customHeight="1">
       <c r="B70" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I70" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="13.5" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="13.5" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B72" s="1"/>
       <c r="H72" s="1"/>
@@ -1543,497 +1546,497 @@
     </row>
     <row r="73" spans="1:9" ht="13.5" customHeight="1">
       <c r="B73" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I73" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="13.5" customHeight="1">
       <c r="B74" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I74" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="13.5" customHeight="1">
       <c r="B75" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="13.5" customHeight="1">
       <c r="B76" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="13.5" customHeight="1">
       <c r="B77" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="13.5" customHeight="1">
       <c r="B78" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="13.5" customHeight="1">
       <c r="B79" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="13.5" customHeight="1">
       <c r="B80" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I80" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1">
       <c r="B81" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I81" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J81" s="1"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" customHeight="1">
       <c r="I82" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1">
       <c r="I83" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="13.5" customHeight="1">
       <c r="I84" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="13.5" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I85" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="J85" s="1"/>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I86" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="J86" s="1"/>
     </row>
     <row r="87" spans="1:10" ht="13.5" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1">
       <c r="B88" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="13.5" customHeight="1">
       <c r="B89" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1">
       <c r="B90" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1">
       <c r="B91" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I91" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="13.5" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1">
       <c r="B94" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I94" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1">
       <c r="B95" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I95" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1">
       <c r="B96" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I96" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="13.5" customHeight="1">
       <c r="B97" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I97" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="13.5" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="13.5" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="13.5" customHeight="1">
       <c r="I100" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="13.5" customHeight="1">
       <c r="I101" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="13.5" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I102" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="13.5" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
     </row>
     <row r="104" spans="1:9" ht="13.5" customHeight="1">
       <c r="B104" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C104" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I104" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="13.5" customHeight="1">
       <c r="B105" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I105" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="13.5" customHeight="1">
       <c r="B106" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="13.5" customHeight="1">
       <c r="I107" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="13.5" customHeight="1">
       <c r="I108" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="13.5" customHeight="1">
       <c r="I109" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="13.5" customHeight="1">
       <c r="I110" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="13.5" customHeight="1">
       <c r="B111" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I111" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="13.5" customHeight="1">
       <c r="B112" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I112" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1">
       <c r="B113" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I113" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1">
       <c r="B114" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1">
       <c r="B115" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C115" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I115" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J116" s="1"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1">
       <c r="A117" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I117" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="J117" s="1"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1">
       <c r="A118" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1">
       <c r="B119" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1">
       <c r="A120" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="B122" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1">
       <c r="B123" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1">
       <c r="B124" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1">
       <c r="A125" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="13.5" customHeight="1">
       <c r="A126" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B126" s="1"/>
       <c r="I126" s="1"/>
@@ -2041,60 +2044,60 @@
     </row>
     <row r="127" spans="1:10" ht="13.5" customHeight="1">
       <c r="B127" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I127" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="13.5" customHeight="1">
       <c r="B128" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="I128" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="13.5" customHeight="1">
       <c r="A129" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="13.5" customHeight="1">
       <c r="A130" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="13.5" customHeight="1">
       <c r="I131" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="13.5" customHeight="1">
       <c r="A132" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="13.5" customHeight="1">
       <c r="A133" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="13.5" customHeight="1">
       <c r="A134" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
@@ -2108,45 +2111,45 @@
     </row>
     <row r="136" spans="1:9" ht="13.5" customHeight="1">
       <c r="I136" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="13.5" customHeight="1">
       <c r="I137" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="13.5" customHeight="1">
       <c r="I138" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="13.5" customHeight="1">
       <c r="I139" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="13.5" customHeight="1">
       <c r="I140" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="13.5" customHeight="1">
       <c r="I141" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="13.5" customHeight="1">
       <c r="I142" s="1" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="13.5" customHeight="1">
       <c r="A143" s="3" t="s">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="13.5" customHeight="1"/>

--- a/Assets/test260903/chapter0101.xlsx
+++ b/Assets/test260903/chapter0101.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="25" documentId="11_78D6C523542A8DBFC7C17204B70FFA00F94AF2BB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB54BD89-8928-4C74-B02F-DD38AC978ABC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3360" yWindow="2976" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chapter0101" sheetId="1" r:id="rId1"/>
